--- a/wooclap/imports/optional/05_Constraints_Part_1_optional.xlsx
+++ b/wooclap/imports/optional/05_Constraints_Part_1_optional.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Questions'!$A$1:$J$3</definedName>

--- a/wooclap/imports/optional/05_Constraints_Part_1_optional.xlsx
+++ b/wooclap/imports/optional/05_Constraints_Part_1_optional.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>L02-O01 · One unassigned exam has 2 possible time slots; another has 5. Which does the “fewest remaining choices first” rule select?</t>
+          <t>L02-O01 · We have already selected variable A. The only rule is A ≠ B, with dom(A) = {1,2} and dom(B) = {1,3}. Which value should least-constraining-value ordering try first, and why?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -530,22 +530,22 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The exam with 5 possible time slots.</t>
+          <t>A = 1: it uses the smaller value and therefore removes fewer choices.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The exam with 2 possible time slots.</t>
+          <t>A = 2: both values of B remain available, whereas A = 1 removes B = 1.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Always the exam with the longer name.</t>
+          <t>A = 1: leaving B only one value is the aim of least-constraining-value ordering.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>It cannot choose unless both have the same number of options.</t>
+          <t>Either value: A has two choices, so both must affect B equally.</t>
         </is>
       </c>
       <c r="H2" s="2" t="n"/>
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>L02-O02 · A class loses one of its possible time slots. Should you recheck related room and teacher rules?</t>
+          <t>L02-O02 · The rules are A &lt; B and B &lt; C. Currently A = {1,2,3}, B = {2,3,4}, C = {3,4}. Checking B &lt; C removes B = 4. When A &lt; B is rechecked, which value of A loses its last support?</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>No. A rule can only be checked once.</t>
+          <t>A = 1, because B = 1 is unavailable.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>No. Removing an option can never affect another class.</t>
+          <t>A = 2, because B must use the same value as A.</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Yes. Fewer options for one class can affect the options for others.</t>
+          <t>A = 3, because its only larger partner was B = 4.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Yes, because removing a slot adds every previously rejected slot back.</t>
+          <t>No value: A’s domain has not changed yet.</t>
         </is>
       </c>
       <c r="H3" s="3" t="n"/>
